--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -16862,7 +16862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24205,6 +24205,16 @@
       </c>
       <c r="B734" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G608"/>
+  <dimension ref="A1:G609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16848,6 +16848,33 @@
       <c r="G608" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>389.39</v>
+      </c>
+      <c r="C609" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="D609" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="E609" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="F609" t="n">
+        <v>388.64</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B735"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24215,6 +24242,16 @@
       </c>
       <c r="B735" t="n">
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
@@ -24383,28 +24420,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06815015842882383</v>
+        <v>0.06459072579037244</v>
       </c>
       <c r="J2" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K2" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01030262512644098</v>
+        <v>0.00922341142699501</v>
       </c>
       <c r="M2" t="n">
-        <v>4.015152885149737</v>
+        <v>4.023327490805098</v>
       </c>
       <c r="N2" t="n">
-        <v>25.54720681650993</v>
+        <v>25.71004888149651</v>
       </c>
       <c r="O2" t="n">
-        <v>5.054424479256756</v>
+        <v>5.07050775381485</v>
       </c>
       <c r="P2" t="n">
-        <v>398.7834234266873</v>
+        <v>398.819459264876</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24465,28 +24502,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1035716872009469</v>
+        <v>0.09844144066895265</v>
       </c>
       <c r="J3" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K3" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01816425669051358</v>
+        <v>0.01628986577097558</v>
       </c>
       <c r="M3" t="n">
-        <v>4.438597949918086</v>
+        <v>4.454281318461992</v>
       </c>
       <c r="N3" t="n">
-        <v>33.20155875911276</v>
+        <v>33.5725230206815</v>
       </c>
       <c r="O3" t="n">
-        <v>5.762079378064204</v>
+        <v>5.794180099089215</v>
       </c>
       <c r="P3" t="n">
-        <v>390.1027188765281</v>
+        <v>390.1546576973103</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24543,28 +24580,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1427937419860213</v>
+        <v>0.1389225355150363</v>
       </c>
       <c r="J4" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K4" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04366857200955643</v>
+        <v>0.04119575889504845</v>
       </c>
       <c r="M4" t="n">
-        <v>3.968790090017249</v>
+        <v>3.982701783390649</v>
       </c>
       <c r="N4" t="n">
-        <v>25.56895335433085</v>
+        <v>25.76921919685175</v>
       </c>
       <c r="O4" t="n">
-        <v>5.05657525943507</v>
+        <v>5.076339153056241</v>
       </c>
       <c r="P4" t="n">
-        <v>384.2080823757753</v>
+        <v>384.2472746246963</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24621,28 +24658,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06118582413113496</v>
+        <v>0.05721008047247401</v>
       </c>
       <c r="J5" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K5" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00628496408313739</v>
+        <v>0.005477334436139514</v>
       </c>
       <c r="M5" t="n">
-        <v>4.697407438238227</v>
+        <v>4.710527408453642</v>
       </c>
       <c r="N5" t="n">
-        <v>33.89345586450995</v>
+        <v>34.09329390345323</v>
       </c>
       <c r="O5" t="n">
-        <v>5.821808642038138</v>
+        <v>5.838946300785205</v>
       </c>
       <c r="P5" t="n">
-        <v>378.4080419831947</v>
+        <v>378.4482925707786</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24699,28 +24736,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09714223063844908</v>
+        <v>0.09494985485463855</v>
       </c>
       <c r="J6" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K6" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01869463371861957</v>
+        <v>0.01789002832585052</v>
       </c>
       <c r="M6" t="n">
-        <v>4.201213455563</v>
+        <v>4.207939161693943</v>
       </c>
       <c r="N6" t="n">
-        <v>27.93484747983084</v>
+        <v>27.96471932622847</v>
       </c>
       <c r="O6" t="n">
-        <v>5.285342702212491</v>
+        <v>5.288167861010888</v>
       </c>
       <c r="P6" t="n">
-        <v>392.881281304101</v>
+        <v>392.9037369646643</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24758,7 +24795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G608"/>
+  <dimension ref="A1:G609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47245,6 +47282,43 @@
         </is>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-36.368853870041924,174.83732770513026</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-36.36921507478441,174.83807679472136</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-36.36935377936593,174.8389333018557</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-36.36949420845008,174.83981094023665</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-36.36934896422639,174.8407172780193</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G609"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16873,6 +16873,87 @@
         <v>388.64</v>
       </c>
       <c r="G609" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>389.73</v>
+      </c>
+      <c r="C610" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="D610" t="n">
+        <v>376.42</v>
+      </c>
+      <c r="E610" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="F610" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>390.9</v>
+      </c>
+      <c r="C611" t="n">
+        <v>378.85</v>
+      </c>
+      <c r="D611" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="E611" t="n">
+        <v>368.48</v>
+      </c>
+      <c r="F611" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="C612" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="D612" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="E612" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="F612" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="G612" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16889,7 +16970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24252,6 +24333,36 @@
       </c>
       <c r="B736" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -24420,28 +24531,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06459072579037244</v>
+        <v>0.05492288387028841</v>
       </c>
       <c r="J2" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K2" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00922341142699501</v>
+        <v>0.006627742052394581</v>
       </c>
       <c r="M2" t="n">
-        <v>4.023327490805098</v>
+        <v>4.043926139949838</v>
       </c>
       <c r="N2" t="n">
-        <v>25.71004888149651</v>
+        <v>26.08738981468472</v>
       </c>
       <c r="O2" t="n">
-        <v>5.07050775381485</v>
+        <v>5.107581601373073</v>
       </c>
       <c r="P2" t="n">
-        <v>398.819459264876</v>
+        <v>398.9177967620755</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24502,28 +24613,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09844144066895265</v>
+        <v>0.08472672497520446</v>
       </c>
       <c r="J3" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K3" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01628986577097558</v>
+        <v>0.01189098341028128</v>
       </c>
       <c r="M3" t="n">
-        <v>4.454281318461992</v>
+        <v>4.494085528540064</v>
       </c>
       <c r="N3" t="n">
-        <v>33.5725230206815</v>
+        <v>34.41957158174996</v>
       </c>
       <c r="O3" t="n">
-        <v>5.794180099089215</v>
+        <v>5.866819545695091</v>
       </c>
       <c r="P3" t="n">
-        <v>390.1546576973103</v>
+        <v>390.2941597268588</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24580,28 +24691,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1389225355150363</v>
+        <v>0.1283915815530887</v>
       </c>
       <c r="J4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04119575889504845</v>
+        <v>0.03498112799737907</v>
       </c>
       <c r="M4" t="n">
-        <v>3.982701783390649</v>
+        <v>4.018303607020402</v>
       </c>
       <c r="N4" t="n">
-        <v>25.76921919685175</v>
+        <v>26.2393230492982</v>
       </c>
       <c r="O4" t="n">
-        <v>5.076339153056241</v>
+        <v>5.122433313309037</v>
       </c>
       <c r="P4" t="n">
-        <v>384.2472746246963</v>
+        <v>384.354391227178</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24658,28 +24769,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05721008047247401</v>
+        <v>0.04601945949931959</v>
       </c>
       <c r="J5" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K5" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005477334436139514</v>
+        <v>0.003519300387675672</v>
       </c>
       <c r="M5" t="n">
-        <v>4.710527408453642</v>
+        <v>4.746020942219185</v>
       </c>
       <c r="N5" t="n">
-        <v>34.09329390345323</v>
+        <v>34.59976216242352</v>
       </c>
       <c r="O5" t="n">
-        <v>5.838946300785205</v>
+        <v>5.882156251105841</v>
       </c>
       <c r="P5" t="n">
-        <v>378.4482925707786</v>
+        <v>378.5621183521887</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24736,28 +24847,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09494985485463855</v>
+        <v>0.08810930084651826</v>
       </c>
       <c r="J6" t="n">
+        <v>611</v>
+      </c>
+      <c r="K6" t="n">
         <v>608</v>
       </c>
-      <c r="K6" t="n">
-        <v>605</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01789002832585052</v>
+        <v>0.01546426131855805</v>
       </c>
       <c r="M6" t="n">
-        <v>4.207939161693943</v>
+        <v>4.229636601853732</v>
       </c>
       <c r="N6" t="n">
-        <v>27.96471932622847</v>
+        <v>28.08909861403472</v>
       </c>
       <c r="O6" t="n">
-        <v>5.288167861010888</v>
+        <v>5.299914962905983</v>
       </c>
       <c r="P6" t="n">
-        <v>392.9037369646643</v>
+        <v>392.9741112134894</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24795,7 +24906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G609"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47319,6 +47430,117 @@
         </is>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-36.36885100554527,174.83732905059537</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-36.36920473172269,174.83808030095093</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-36.369348326143616,174.8389341632772</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-36.369492949361984,174.83981104115335</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-36.36936354617275,174.8407163800359</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-36.36884114830667,174.8373336805775</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-36.36919647465652,174.8380831000411</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-36.36934180015622,174.83893519415855</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-36.36948557470307,174.8398116322369</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-36.36936354617275,174.8407163800359</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-36.368845613551535,174.8373315832353</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-36.369202471894056,174.83808106701778</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-36.36934403508341,174.838934841117</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-36.369486743856314,174.83981153852855</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-36.36932907157113,174.8407185030457</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16956,6 +16956,33 @@
       <c r="G612" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>391.73</v>
+      </c>
+      <c r="C613" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="D613" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="E613" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="F613" t="n">
+        <v>391.4</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24363,6 +24390,16 @@
       </c>
       <c r="B739" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -24531,28 +24568,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05492288387028841</v>
+        <v>0.05218522780023779</v>
       </c>
       <c r="J2" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K2" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006627742052394581</v>
+        <v>0.005980804127796668</v>
       </c>
       <c r="M2" t="n">
-        <v>4.043926139949838</v>
+        <v>4.048841969785136</v>
       </c>
       <c r="N2" t="n">
-        <v>26.08738981468472</v>
+        <v>26.16633011541358</v>
       </c>
       <c r="O2" t="n">
-        <v>5.107581601373073</v>
+        <v>5.115303521338062</v>
       </c>
       <c r="P2" t="n">
-        <v>398.9177967620755</v>
+        <v>398.9457378006632</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24613,28 +24650,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08472672497520446</v>
+        <v>0.08074995267315534</v>
       </c>
       <c r="J3" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K3" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01189098341028128</v>
+        <v>0.01077131051738278</v>
       </c>
       <c r="M3" t="n">
-        <v>4.494085528540064</v>
+        <v>4.505376844388667</v>
       </c>
       <c r="N3" t="n">
-        <v>34.41957158174996</v>
+        <v>34.61984883815117</v>
       </c>
       <c r="O3" t="n">
-        <v>5.866819545695091</v>
+        <v>5.883863427897623</v>
       </c>
       <c r="P3" t="n">
-        <v>390.2941597268588</v>
+        <v>390.334747421406</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24691,28 +24728,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1283915815530887</v>
+        <v>0.1252947679216457</v>
       </c>
       <c r="J4" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K4" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03498112799737907</v>
+        <v>0.03329348955554734</v>
       </c>
       <c r="M4" t="n">
-        <v>4.018303607020402</v>
+        <v>4.027984694635306</v>
       </c>
       <c r="N4" t="n">
-        <v>26.2393230492982</v>
+        <v>26.35200448947527</v>
       </c>
       <c r="O4" t="n">
-        <v>5.122433313309037</v>
+        <v>5.133420349968943</v>
       </c>
       <c r="P4" t="n">
-        <v>384.354391227178</v>
+        <v>384.3859978961536</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24769,28 +24806,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04601945949931959</v>
+        <v>0.04278947605674881</v>
       </c>
       <c r="J5" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K5" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003519300387675672</v>
+        <v>0.003040036924863987</v>
       </c>
       <c r="M5" t="n">
-        <v>4.746020942219185</v>
+        <v>4.755234341234543</v>
       </c>
       <c r="N5" t="n">
-        <v>34.59976216242352</v>
+        <v>34.71244892182435</v>
       </c>
       <c r="O5" t="n">
-        <v>5.882156251105841</v>
+        <v>5.891727159485947</v>
       </c>
       <c r="P5" t="n">
-        <v>378.5621183521887</v>
+        <v>378.5950841775873</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24847,28 +24884,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08810930084651826</v>
+        <v>0.08685376489241681</v>
       </c>
       <c r="J6" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K6" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01546426131855805</v>
+        <v>0.01507313406257071</v>
       </c>
       <c r="M6" t="n">
-        <v>4.229636601853732</v>
+        <v>4.230468938365661</v>
       </c>
       <c r="N6" t="n">
-        <v>28.08909861403472</v>
+        <v>28.06799384059343</v>
       </c>
       <c r="O6" t="n">
-        <v>5.299914962905983</v>
+        <v>5.297923540463135</v>
       </c>
       <c r="P6" t="n">
-        <v>392.9741112134894</v>
+        <v>392.987074156967</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24906,7 +24943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47541,6 +47578,43 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-36.36883415556466,174.83733696509407</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-36.36918665309355,174.8380864294845</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-36.36933438019794,174.83893636625635</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-36.36947568186793,174.83981242515372</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-36.36932412091031,174.8407188079165</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G613"/>
+  <dimension ref="A1:G615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16981,6 +16981,60 @@
         <v>391.4</v>
       </c>
       <c r="G613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="C614" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="D614" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="E614" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="F614" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>397.16</v>
+      </c>
+      <c r="C615" t="n">
+        <v>384.04</v>
+      </c>
+      <c r="D615" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="E615" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="F615" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="G615" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16997,7 +17051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24400,6 +24454,26 @@
       </c>
       <c r="B740" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -24568,28 +24642,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05218522780023779</v>
+        <v>0.04955848924805998</v>
       </c>
       <c r="J2" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K2" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005980804127796668</v>
+        <v>0.005423065873116362</v>
       </c>
       <c r="M2" t="n">
-        <v>4.048841969785136</v>
+        <v>4.047089077046005</v>
       </c>
       <c r="N2" t="n">
-        <v>26.16633011541358</v>
+        <v>26.14045670785728</v>
       </c>
       <c r="O2" t="n">
-        <v>5.115303521338062</v>
+        <v>5.11277387607327</v>
       </c>
       <c r="P2" t="n">
-        <v>398.9457378006632</v>
+        <v>398.9726083463257</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24650,28 +24724,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08074995267315534</v>
+        <v>0.07518663498388284</v>
       </c>
       <c r="J3" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K3" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01077131051738278</v>
+        <v>0.009350045690246334</v>
       </c>
       <c r="M3" t="n">
-        <v>4.505376844388667</v>
+        <v>4.517043011456617</v>
       </c>
       <c r="N3" t="n">
-        <v>34.61984883815117</v>
+        <v>34.75932525065593</v>
       </c>
       <c r="O3" t="n">
-        <v>5.883863427897623</v>
+        <v>5.895703965656343</v>
       </c>
       <c r="P3" t="n">
-        <v>390.334747421406</v>
+        <v>390.3916628241352</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24728,28 +24802,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1252947679216457</v>
+        <v>0.1210196606113759</v>
       </c>
       <c r="J4" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03329348955554734</v>
+        <v>0.03117062363389167</v>
       </c>
       <c r="M4" t="n">
-        <v>4.027984694635306</v>
+        <v>4.037249287956858</v>
       </c>
       <c r="N4" t="n">
-        <v>26.35200448947527</v>
+        <v>26.4178347350191</v>
       </c>
       <c r="O4" t="n">
-        <v>5.133420349968943</v>
+        <v>5.139828278748142</v>
       </c>
       <c r="P4" t="n">
-        <v>384.3859978961536</v>
+        <v>384.4297324702328</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24806,28 +24880,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04278947605674881</v>
+        <v>0.03744348912535547</v>
       </c>
       <c r="J5" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K5" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003040036924863987</v>
+        <v>0.002330399125941796</v>
       </c>
       <c r="M5" t="n">
-        <v>4.755234341234543</v>
+        <v>4.768007831570122</v>
       </c>
       <c r="N5" t="n">
-        <v>34.71244892182435</v>
+        <v>34.83313822764219</v>
       </c>
       <c r="O5" t="n">
-        <v>5.891727159485947</v>
+        <v>5.901960541010267</v>
       </c>
       <c r="P5" t="n">
-        <v>378.5950841775873</v>
+        <v>378.649775485515</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24884,28 +24958,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08685376489241681</v>
+        <v>0.0816734532819523</v>
       </c>
       <c r="J6" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K6" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01507313406257071</v>
+        <v>0.01332565622721893</v>
       </c>
       <c r="M6" t="n">
-        <v>4.230468938365661</v>
+        <v>4.248959965603086</v>
       </c>
       <c r="N6" t="n">
-        <v>28.06799384059343</v>
+        <v>28.23353970737959</v>
       </c>
       <c r="O6" t="n">
-        <v>5.297923540463135</v>
+        <v>5.313524226667231</v>
       </c>
       <c r="P6" t="n">
-        <v>392.987074156967</v>
+        <v>393.0406959120446</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24943,7 +25017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G613"/>
+  <dimension ref="A1:G615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47615,6 +47689,80 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-36.36880517359689,174.83735057802417</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-36.369158231401975,174.83809606424103</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-36.36931659017745,174.8389391764659</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-36.36946641857684,174.83981316761205</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-36.36932907157113,174.8407185030457</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-36.36878840786491,174.83735845294152</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-36.36915136499931,174.83809839190297</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-36.3692994259365,174.83894188782284</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-36.36945508678381,174.8398140758619</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-36.36939505037773,174.84071443994753</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G615"/>
+  <dimension ref="A1:G619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17035,6 +17035,114 @@
         <v>383.52</v>
       </c>
       <c r="G615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>397.72</v>
+      </c>
+      <c r="C616" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="D616" t="n">
+        <v>385.28</v>
+      </c>
+      <c r="E616" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="F616" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>398.82</v>
+      </c>
+      <c r="C617" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="D617" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="E617" t="n">
+        <v>373.99</v>
+      </c>
+      <c r="F617" t="n">
+        <v>386.67</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>398.21</v>
+      </c>
+      <c r="C618" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="D618" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="E618" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="F618" t="n">
+        <v>386.67</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>397.16</v>
+      </c>
+      <c r="C619" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="D619" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="E619" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="F619" t="n">
+        <v>386.67</v>
+      </c>
+      <c r="G619" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17051,7 +17159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B742"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24474,6 +24582,46 @@
       </c>
       <c r="B742" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -24642,28 +24790,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04955848924805998</v>
+        <v>0.04667558403035833</v>
       </c>
       <c r="J2" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K2" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005423065873116362</v>
+        <v>0.004874808070589154</v>
       </c>
       <c r="M2" t="n">
-        <v>4.047089077046005</v>
+        <v>4.0334283496985</v>
       </c>
       <c r="N2" t="n">
-        <v>26.14045670785728</v>
+        <v>26.00780071184644</v>
       </c>
       <c r="O2" t="n">
-        <v>5.11277387607327</v>
+        <v>5.099784378956275</v>
       </c>
       <c r="P2" t="n">
-        <v>398.9726083463257</v>
+        <v>399.0022159765552</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24724,28 +24872,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07518663498388284</v>
+        <v>0.07250293225547913</v>
       </c>
       <c r="J3" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K3" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009350045690246334</v>
+        <v>0.00881476221953037</v>
       </c>
       <c r="M3" t="n">
-        <v>4.517043011456617</v>
+        <v>4.500465036666393</v>
       </c>
       <c r="N3" t="n">
-        <v>34.75932525065593</v>
+        <v>34.56680772833038</v>
       </c>
       <c r="O3" t="n">
-        <v>5.895703965656343</v>
+        <v>5.879354363221389</v>
       </c>
       <c r="P3" t="n">
-        <v>390.3916628241352</v>
+        <v>390.4192118213277</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24802,28 +24950,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1210196606113759</v>
+        <v>0.1193380742060989</v>
       </c>
       <c r="J4" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K4" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03117062363389167</v>
+        <v>0.03073897016028115</v>
       </c>
       <c r="M4" t="n">
-        <v>4.037249287956858</v>
+        <v>4.019849456248054</v>
       </c>
       <c r="N4" t="n">
-        <v>26.4178347350191</v>
+        <v>26.26112922690238</v>
       </c>
       <c r="O4" t="n">
-        <v>5.139828278748142</v>
+        <v>5.124561369220041</v>
       </c>
       <c r="P4" t="n">
-        <v>384.4297324702328</v>
+        <v>384.4469922491267</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24880,28 +25028,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03744348912535547</v>
+        <v>0.02946290877550736</v>
       </c>
       <c r="J5" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K5" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002330399125941796</v>
+        <v>0.001453625806754011</v>
       </c>
       <c r="M5" t="n">
-        <v>4.768007831570122</v>
+        <v>4.779144814748597</v>
       </c>
       <c r="N5" t="n">
-        <v>34.83313822764219</v>
+        <v>34.87151088297033</v>
       </c>
       <c r="O5" t="n">
-        <v>5.901960541010267</v>
+        <v>5.905210485915835</v>
       </c>
       <c r="P5" t="n">
-        <v>378.649775485515</v>
+        <v>378.7317198291192</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24958,28 +25106,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0816734532819523</v>
+        <v>0.07063653906024628</v>
       </c>
       <c r="J6" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K6" t="n">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01332565622721893</v>
+        <v>0.009970393209497774</v>
       </c>
       <c r="M6" t="n">
-        <v>4.248959965603086</v>
+        <v>4.290465106355474</v>
       </c>
       <c r="N6" t="n">
-        <v>28.23353970737959</v>
+        <v>28.54040615237678</v>
       </c>
       <c r="O6" t="n">
-        <v>5.313524226667231</v>
+        <v>5.342322168530907</v>
       </c>
       <c r="P6" t="n">
-        <v>393.0406959120446</v>
+        <v>393.1553263057876</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25017,7 +25165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G615"/>
+  <dimension ref="A1:G619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47763,6 +47911,154 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-36.36878368986989,174.8373606689981</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-36.36910729833824,174.83811333017968</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-36.369269120323374,174.8389466750599</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-36.36945014036623,174.83981447232009</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-36.36937434761446,174.84071571486285</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-36.36877442237957,174.83736502196555</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-36.369092174868356,174.8381184569219</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>-36.369255084980345,174.83894889215682</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-36.36943602059235,174.83981560402785</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-36.369366696593254,174.8407161860271</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-36.36877956162422,174.83736260804733</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-36.36909521694566,174.83811742568082</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-36.36925499558324,174.83894890627846</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-36.369440247531024,174.83981526523638</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-36.369366696593254,174.8407161860271</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-36.36878840786491,174.83735845294152</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-36.36909530386215,174.83811739621675</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-36.369260627599886,174.83894801661543</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-36.369445104013764,174.83981487598658</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-36.369366696593254,174.8407161860271</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G619"/>
+  <dimension ref="A1:G624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17143,6 +17143,141 @@
         <v>386.67</v>
       </c>
       <c r="G619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="C620" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="D620" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="E620" t="n">
+        <v>372.51</v>
+      </c>
+      <c r="F620" t="n">
+        <v>390.19</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>396.31</v>
+      </c>
+      <c r="C621" t="n">
+        <v>389.56</v>
+      </c>
+      <c r="D621" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="E621" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="F621" t="n">
+        <v>392.41</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>396.28</v>
+      </c>
+      <c r="C622" t="n">
+        <v>389.97</v>
+      </c>
+      <c r="D622" t="n">
+        <v>385.7</v>
+      </c>
+      <c r="E622" t="n">
+        <v>372.12</v>
+      </c>
+      <c r="F622" t="n">
+        <v>394.62</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>396.14</v>
+      </c>
+      <c r="C623" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="D623" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="E623" t="n">
+        <v>372.12</v>
+      </c>
+      <c r="F623" t="n">
+        <v>394.62</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>396.06</v>
+      </c>
+      <c r="C624" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="D624" t="n">
+        <v>385.55</v>
+      </c>
+      <c r="E624" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="F624" t="n">
+        <v>395.79</v>
+      </c>
+      <c r="G624" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17159,7 +17294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B746"/>
+  <dimension ref="A1:B751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24622,6 +24757,56 @@
       </c>
       <c r="B746" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -24790,28 +24975,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04667558403035833</v>
+        <v>0.04067747109281347</v>
       </c>
       <c r="J2" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="K2" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004874808070589154</v>
+        <v>0.003754199627287957</v>
       </c>
       <c r="M2" t="n">
-        <v>4.0334283496985</v>
+        <v>4.027469198304415</v>
       </c>
       <c r="N2" t="n">
-        <v>26.00780071184644</v>
+        <v>25.92029031012832</v>
       </c>
       <c r="O2" t="n">
-        <v>5.099784378956275</v>
+        <v>5.091197335610585</v>
       </c>
       <c r="P2" t="n">
-        <v>399.0022159765552</v>
+        <v>399.0640852346535</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24872,28 +25057,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07250293225547913</v>
+        <v>0.06838906253193311</v>
       </c>
       <c r="J3" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="K3" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00881476221953037</v>
+        <v>0.007974254625868982</v>
       </c>
       <c r="M3" t="n">
-        <v>4.500465036666393</v>
+        <v>4.483529954346941</v>
       </c>
       <c r="N3" t="n">
-        <v>34.56680772833038</v>
+        <v>34.34701304308784</v>
       </c>
       <c r="O3" t="n">
-        <v>5.879354363221389</v>
+        <v>5.860632478076734</v>
       </c>
       <c r="P3" t="n">
-        <v>390.4192118213277</v>
+        <v>390.4616462487685</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24950,28 +25135,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1193380742060989</v>
+        <v>0.1162812669075745</v>
       </c>
       <c r="J4" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="K4" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03073897016028115</v>
+        <v>0.02969427126021529</v>
       </c>
       <c r="M4" t="n">
-        <v>4.019849456248054</v>
+        <v>4.003215651244012</v>
       </c>
       <c r="N4" t="n">
-        <v>26.26112922690238</v>
+        <v>26.08184222054541</v>
       </c>
       <c r="O4" t="n">
-        <v>5.124561369220041</v>
+        <v>5.107038498048102</v>
       </c>
       <c r="P4" t="n">
-        <v>384.4469922491267</v>
+        <v>384.4785202468686</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25028,28 +25213,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02946290877550736</v>
+        <v>0.01809047468245256</v>
       </c>
       <c r="J5" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="K5" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001453625806754011</v>
+        <v>0.0005512545723771467</v>
       </c>
       <c r="M5" t="n">
-        <v>4.779144814748597</v>
+        <v>4.80097706844706</v>
       </c>
       <c r="N5" t="n">
-        <v>34.87151088297033</v>
+        <v>35.02604307043759</v>
       </c>
       <c r="O5" t="n">
-        <v>5.905210485915835</v>
+        <v>5.918280414988597</v>
       </c>
       <c r="P5" t="n">
-        <v>378.7317198291192</v>
+        <v>378.8490195331668</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25106,28 +25291,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07063653906024628</v>
+        <v>0.06828697158917006</v>
       </c>
       <c r="J6" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="K6" t="n">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009970393209497774</v>
+        <v>0.009471232196430535</v>
       </c>
       <c r="M6" t="n">
-        <v>4.290465106355474</v>
+        <v>4.272955575082096</v>
       </c>
       <c r="N6" t="n">
-        <v>28.54040615237678</v>
+        <v>28.36046513293734</v>
       </c>
       <c r="O6" t="n">
-        <v>5.342322168530907</v>
+        <v>5.325454453184004</v>
       </c>
       <c r="P6" t="n">
-        <v>393.1553263057876</v>
+        <v>393.1798010286308</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25165,7 +25350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G619"/>
+  <dimension ref="A1:G624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48059,6 +48244,191 @@
         </is>
       </c>
     </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-36.36879110386206,174.83735718662336</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-36.36909904127138,174.8381161292633</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-36.36926473986599,174.83894736702015</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-36.36944933095244,174.83981453719505</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-36.369335012364104,174.84071813720075</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-36.36879556910728,174.83735508928376</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-36.369103387096054,174.83811465606146</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-36.36926777936702,174.8389468868845</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-36.369453198151646,174.83981422723684</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-36.36931502969679,174.84071936777</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.368795821857006,174.8373549705664</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.369099823519825,174.83811586408697</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.369265365645624,174.8389472681687</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.36945283841218,174.83981425607016</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.369295137041426,174.84072059279572</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-36.36879700135574,174.83735441655213</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-36.36910260484762,174.8381149212378</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-36.36926473986599,174.83894736702015</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-36.36945283841218,174.83981425607016</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-36.369295137041426,174.84072059279572</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-36.36879767535502,174.83735409997252</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-36.369107211421756,174.83811335964373</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-36.369266706601955,174.83894705634413</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-36.36945796469951,174.83981384519527</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-36.36928460563563,174.84072124133857</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G624"/>
+  <dimension ref="A1:G629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17280,6 +17280,141 @@
       <c r="G624" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>395.22</v>
+      </c>
+      <c r="C625" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="D625" t="n">
+        <v>384.53</v>
+      </c>
+      <c r="E625" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="F625" t="n">
+        <v>395.79</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>395.37</v>
+      </c>
+      <c r="C626" t="n">
+        <v>388.11</v>
+      </c>
+      <c r="D626" t="n">
+        <v>385.09</v>
+      </c>
+      <c r="E626" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="F626" t="n">
+        <v>397.87</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>397.49</v>
+      </c>
+      <c r="C627" t="n">
+        <v>388.08</v>
+      </c>
+      <c r="D627" t="n">
+        <v>385.27</v>
+      </c>
+      <c r="E627" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="F627" t="n">
+        <v>397.87</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>397.21</v>
+      </c>
+      <c r="C628" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="D628" t="n">
+        <v>384.85</v>
+      </c>
+      <c r="E628" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="F628" t="n">
+        <v>397.87</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>396.73</v>
+      </c>
+      <c r="C629" t="n">
+        <v>387.06</v>
+      </c>
+      <c r="D629" t="n">
+        <v>384.19</v>
+      </c>
+      <c r="E629" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="F629" t="n">
+        <v>397.87</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B751"/>
+  <dimension ref="A1:B756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24807,6 +24942,56 @@
       </c>
       <c r="B751" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -24975,28 +25160,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04067747109281347</v>
+        <v>0.03503912031678685</v>
       </c>
       <c r="J2" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="K2" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003754199627287957</v>
+        <v>0.002823676984274659</v>
       </c>
       <c r="M2" t="n">
-        <v>4.027469198304415</v>
+        <v>4.020599564394788</v>
       </c>
       <c r="N2" t="n">
-        <v>25.92029031012832</v>
+        <v>25.83037498793877</v>
       </c>
       <c r="O2" t="n">
-        <v>5.091197335610585</v>
+        <v>5.082359195092253</v>
       </c>
       <c r="P2" t="n">
-        <v>399.0640852346535</v>
+        <v>399.122478745268</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -25057,28 +25242,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06838906253193311</v>
+        <v>0.06162127933723342</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="K3" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007974254625868982</v>
+        <v>0.006564952840370397</v>
       </c>
       <c r="M3" t="n">
-        <v>4.483529954346941</v>
+        <v>4.479221623416709</v>
       </c>
       <c r="N3" t="n">
-        <v>34.34701304308784</v>
+        <v>34.23234622982584</v>
       </c>
       <c r="O3" t="n">
-        <v>5.860632478076734</v>
+        <v>5.850841497581851</v>
       </c>
       <c r="P3" t="n">
-        <v>390.4616462487685</v>
+        <v>390.5317583515189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25135,28 +25320,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1162812669075745</v>
+        <v>0.1120403996315785</v>
       </c>
       <c r="J4" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="K4" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02969427126021529</v>
+        <v>0.02802513692989184</v>
       </c>
       <c r="M4" t="n">
-        <v>4.003215651244012</v>
+        <v>3.992953898221047</v>
       </c>
       <c r="N4" t="n">
-        <v>26.08184222054541</v>
+        <v>25.93725231801979</v>
       </c>
       <c r="O4" t="n">
-        <v>5.107038498048102</v>
+        <v>5.092862880347338</v>
       </c>
       <c r="P4" t="n">
-        <v>384.4785202468686</v>
+        <v>384.5224520730877</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25213,28 +25398,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01809047468245256</v>
+        <v>0.005373919326451398</v>
       </c>
       <c r="J5" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="K5" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005512545723771467</v>
+        <v>4.873109816827537e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.80097706844706</v>
+        <v>4.83054531634692</v>
       </c>
       <c r="N5" t="n">
-        <v>35.02604307043759</v>
+        <v>35.30386880899144</v>
       </c>
       <c r="O5" t="n">
-        <v>5.918280414988597</v>
+        <v>5.941705883750174</v>
       </c>
       <c r="P5" t="n">
-        <v>378.8490195331668</v>
+        <v>378.9807439888721</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25291,28 +25476,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06828697158917006</v>
+        <v>0.0719971055776945</v>
       </c>
       <c r="J6" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="K6" t="n">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009471232196430535</v>
+        <v>0.01067915407270903</v>
       </c>
       <c r="M6" t="n">
-        <v>4.272955575082096</v>
+        <v>4.254001090390291</v>
       </c>
       <c r="N6" t="n">
-        <v>28.36046513293734</v>
+        <v>28.18535730600025</v>
       </c>
       <c r="O6" t="n">
-        <v>5.325454453184004</v>
+        <v>5.308988350524067</v>
       </c>
       <c r="P6" t="n">
-        <v>393.1798010286308</v>
+        <v>393.1409158361729</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25350,7 +25535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G624"/>
+  <dimension ref="A1:G629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48429,6 +48614,191 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-36.36880475234735,174.83735077588645</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-36.36911642456996,174.83811023645504</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-36.369275825105056,174.83894561593692</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-36.36946695818603,174.83981312436205</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-36.36928460563563,174.84072124133857</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-36.36880348859873,174.8373513694733</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-36.36911598998751,174.83811038377527</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-36.36927081886805,174.83894640674876</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-36.36946452994467,174.83981331898704</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-36.369265883136386,174.84072239430338</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-36.36878562761786,174.837359758832</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-36.36911625073698,174.83811029538313</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-36.36926920972045,174.83894666093826</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-36.369462011768434,174.83981352082034</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-36.369265883136386,174.84072239430338</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-36.36878798661536,174.83735865080374</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-36.369119640480164,174.83810914628523</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-36.3692729643982,174.83894606782943</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-36.36946246144277,174.8398134847787</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-36.369265883136386,174.84072239430338</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-36.36879203061107,174.8373567513265</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-36.36912511621915,174.83810729004998</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-36.36927886460608,174.83894513580114</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-36.36946444000979,174.83981332619535</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-36.369265883136386,174.84072239430338</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
